--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-164</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 549.825,46</t>
-  </si>
-  <si>
-    <t>R$ 3.088,91
-R$ 3.194,41</t>
-  </si>
-  <si>
-    <t>(0.1%)
-2.5%</t>
-  </si>
-  <si>
-    <t>36.5</t>
-  </si>
-  <si>
-    <t>(2.9%)</t>
-  </si>
-  <si>
-    <t>1914.1%</t>
-  </si>
-  <si>
-    <t>1865.0%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
+166</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 555.501,80</t>
+  </si>
+  <si>
+    <t>R$ 3.086,12
+R$ 3.190,11</t>
+  </si>
+  <si>
+    <t>0.2%
+2.7%</t>
+  </si>
+  <si>
+    <t>36.6</t>
+  </si>
+  <si>
+    <t>(2.3%)</t>
+  </si>
+  <si>
+    <t>1894.4%</t>
+  </si>
+  <si>
+    <t>1845.5%</t>
+  </si>
+  <si>
+    <t>4.6%</t>
   </si>
   <si>
     <t>0.0%</t>
@@ -953,22 +953,22 @@
     <t>74.5%</t>
   </si>
   <si>
-    <t>7.7%</t>
+    <t>7.6%</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>11.6</t>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>11.5</t>
   </si>
   <si>
     <t>17.9</t>
   </si>
   <si>
-    <t>75.8%</t>
+    <t>75.9%</t>
   </si>
   <si>
     <t>-R$ 21.084,57</t>
@@ -2118,10 +2118,10 @@
         <v>0.77142857142857135</v>
       </c>
       <c r="T6" s="6">
-        <v>0.31654919966987105</v>
+        <v>0.33087353970265149</v>
       </c>
       <c r="U6" s="6">
-        <v>-0.0024181012937798596</v>
+        <v>0.011906238739000544</v>
       </c>
       <c r="V6" s="6">
         <v>0.032874911365036556</v>
@@ -5924,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>2943.6700000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2943.6700000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.77094814101792797</v>
+      </c>
+      <c r="R36" s="7">
+        <v>49</v>
+      </c>
+      <c r="S36" s="6">
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.30829970750797475</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.0067729738727506815</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.10403645789100001</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.035312721874394888</v>
+      </c>
+      <c r="X36" s="8">
+        <v>26.126345161290324</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.8048155555555558</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.4682806451612898</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>18.54032258064516</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.70967741935483875</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6359,7 +6393,9 @@
       <c r="AB39" s="8">
         <v>2.0166599999999999</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>4.2566660000000001</v>
+      </c>
       <c r="AD39" s="8">
         <v>6.5966649999999998</v>
       </c>
@@ -6672,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6708,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2732.6700000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2732.6700000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.10643371932950041</v>
+      </c>
+      <c r="R42" s="7">
+        <v>34</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.30732023991188107</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.021391093692249702</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.073507595135892737</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.020003147105212119</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.116048148148145</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.48148148148148145</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.0626272727272728</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.2771592592592595</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>10.96111</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>17.887037037037036</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.85185185185185186</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7477,7 +7549,7 @@
         <v>0.054232050509216659</v>
       </c>
       <c r="W48" s="6">
-        <v>-0.0035648339097052572</v>
+        <v>-0.0056524635933881146</v>
       </c>
       <c r="X48" s="8">
         <v>27.443652380952379</v>
@@ -11476,10 +11548,10 @@
         <v>0.024390243902439046</v>
       </c>
       <c r="T80" s="6">
-        <v>-0.25031403544876907</v>
+        <v>-0.20957796328214098</v>
       </c>
       <c r="U80" s="6">
-        <v>-0.53188907896654913</v>
+        <v>-0.49098150815904779</v>
       </c>
       <c r="V80" s="6">
         <v>0.035846217168728933</v>
@@ -13097,10 +13169,10 @@
         <v>0.30769230769230771</v>
       </c>
       <c r="T93" s="6">
-        <v>0.97500386957927598</v>
+        <v>0.33119347366300733</v>
       </c>
       <c r="U93" s="6">
-        <v>0.68926194401301877</v>
+        <v>0.045451548096750082</v>
       </c>
       <c r="V93" s="6">
         <v>0.068836767364074403</v>
@@ -23311,7 +23383,9 @@
       <c r="AB175" s="8">
         <v>2.82916875</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>7.0718740000000002</v>
+      </c>
       <c r="AD175" s="8">
         <v>14.03541875</v>
       </c>
@@ -23954,7 +24028,9 @@
       <c r="AB180" s="8">
         <v>8.6111111111111107</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>12.112626000000001</v>
+      </c>
       <c r="AD180" s="8">
         <v>17.604545454545455</v>
       </c>
@@ -25851,7 +25927,9 @@
       <c r="AB195" s="8">
         <v>6.1279999999999992</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>11.031333</v>
+      </c>
       <c r="AD195" s="8">
         <v>17.968</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 555.501,80</t>
-  </si>
-  <si>
-    <t>R$ 3.086,12
-R$ 3.190,11</t>
-  </si>
-  <si>
-    <t>0.2%
-2.7%</t>
-  </si>
-  <si>
-    <t>36.6</t>
-  </si>
-  <si>
-    <t>(2.3%)</t>
-  </si>
-  <si>
-    <t>1894.4%</t>
-  </si>
-  <si>
-    <t>1845.5%</t>
+167</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 556.987,39</t>
+  </si>
+  <si>
+    <t>R$ 3.077,28
+R$ 3.179,91</t>
+  </si>
+  <si>
+    <t>0.1%
+2.6%</t>
+  </si>
+  <si>
+    <t>36.5</t>
+  </si>
+  <si>
+    <t>(2.4%)</t>
+  </si>
+  <si>
+    <t>1889.4%</t>
+  </si>
+  <si>
+    <t>1840.5%</t>
   </si>
   <si>
     <t>4.6%</t>
@@ -950,25 +950,25 @@
     <t>26.1</t>
   </si>
   <si>
-    <t>74.5%</t>
-  </si>
-  <si>
-    <t>7.6%</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>11.5</t>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>11.6</t>
   </si>
   <si>
     <t>17.9</t>
   </si>
   <si>
-    <t>75.9%</t>
+    <t>75.7%</t>
   </si>
   <si>
     <t>-R$ 21.084,57</t>
@@ -6002,7 +6002,9 @@
       <c r="AB36" s="8">
         <v>5.4682806451612898</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>11.475049</v>
+      </c>
       <c r="AD36" s="8">
         <v>18.54032258064516</v>
       </c>
@@ -14254,7 +14256,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14290,25 +14292,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>1485.5899999999999</v>
+      </c>
+      <c r="P102" s="5">
+        <v>1485.5899999999999</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.28411511290586844</v>
+      </c>
+      <c r="R102" s="7">
+        <v>19</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.26923076923076927</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.37568912014755085</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.034399464185946325</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.016523064910237684</v>
+      </c>
+      <c r="X102" s="8">
+        <v>36.973608333333331</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.3241649999999998</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>11.140909090909091</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>18.430651999999998</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>23.844441666666668</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.16666666666666666</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20787,7 +20825,7 @@
         <v>0.018566455721910364</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.030922971315304189</v>
+        <v>-0.025581655117508956</v>
       </c>
       <c r="X154" s="8">
         <v>21.856864705882355</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -911,55 +911,58 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-167</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 556.987,39</t>
-  </si>
-  <si>
-    <t>R$ 3.077,28
-R$ 3.179,91</t>
-  </si>
-  <si>
-    <t>0.1%
-2.6%</t>
-  </si>
-  <si>
-    <t>36.5</t>
-  </si>
-  <si>
-    <t>(2.4%)</t>
-  </si>
-  <si>
-    <t>1889.4%</t>
-  </si>
-  <si>
-    <t>1840.5%</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+169</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 564.982,29</t>
+  </si>
+  <si>
+    <t>R$ 3.087,33
+R$ 3.189,58</t>
+  </si>
+  <si>
+    <t>0.6%
+3.1%</t>
+  </si>
+  <si>
+    <t>36.7</t>
+  </si>
+  <si>
+    <t>(1.8%)</t>
+  </si>
+  <si>
+    <t>1862.7%</t>
+  </si>
+  <si>
+    <t>1814.0%</t>
   </si>
   <si>
     <t>4.6%</t>
   </si>
   <si>
-    <t>0.0%</t>
+    <t>0.1%</t>
   </si>
   <si>
     <t>26.1</t>
   </si>
   <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
+    <t>74.0%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
   </si>
   <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>7.1</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>11.6</t>
@@ -968,7 +971,7 @@
     <t>17.9</t>
   </si>
   <si>
-    <t>75.7%</t>
+    <t>75.8%</t>
   </si>
   <si>
     <t>-R$ 21.084,57</t>
@@ -2249,10 +2252,10 @@
         <v>-0.125</v>
       </c>
       <c r="T7" s="6">
-        <v>0.41115448577680525</v>
+        <v>0.40015839876431969</v>
       </c>
       <c r="U7" s="6">
-        <v>-0.013597734586175827</v>
+        <v>-0.024593821598661348</v>
       </c>
       <c r="V7" s="6">
         <v>0.064612691466083144</v>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>6315.8599999999997</v>
+      </c>
+      <c r="P34" s="5">
+        <v>6315.8599999999997</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.44501566078443489</v>
+      </c>
+      <c r="R34" s="7">
+        <v>88</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.54385964912280693</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0.0077253137339966379</v>
+      </c>
+      <c r="U34" s="6">
+        <v>-0.3515654241860966</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.057379675926952152</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.022035320605586571</v>
+      </c>
+      <c r="X34" s="8">
+        <v>23.218545070422532</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.49295774647887325</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.070422535211267609</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>10.521590909090909</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.8905477611940298</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>12.907213</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>18.465961971830986</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.80281690140845074</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>0</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -16018,7 +16057,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>16.603570000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19131,7 +19172,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19167,25 +19208,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>1679.04</v>
+      </c>
+      <c r="P141" s="5">
+        <v>1679.04</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.61772810482705443</v>
+      </c>
+      <c r="R141" s="7">
+        <v>19</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.46153846153846145</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.29192747045931006</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.03067949542595769</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.20213097960739473</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.081061797217457598</v>
+      </c>
+      <c r="X141" s="8">
+        <v>15.854764285714285</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>2.79</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.0384615384615383</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>4.8562380000000003</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>12.395235714285715</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28301,112 +28378,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -915,17 +915,17 @@
   </si>
   <si>
     <t>215
-169</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 564.982,29</t>
-  </si>
-  <si>
-    <t>R$ 3.087,33
-R$ 3.189,58</t>
+170</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 569.249,16</t>
+  </si>
+  <si>
+    <t>R$ 3.093,75
+R$ 3.195,92</t>
   </si>
   <si>
     <t>0.6%
@@ -938,10 +938,10 @@
     <t>(1.8%)</t>
   </si>
   <si>
-    <t>1862.7%</t>
-  </si>
-  <si>
-    <t>1814.0%</t>
+    <t>1849.0%</t>
+  </si>
+  <si>
+    <t>1800.4%</t>
   </si>
   <si>
     <t>4.6%</t>
@@ -968,10 +968,10 @@
     <t>11.6</t>
   </si>
   <si>
-    <t>17.9</t>
-  </si>
-  <si>
-    <t>75.8%</t>
+    <t>18.0</t>
+  </si>
+  <si>
+    <t>75.6%</t>
   </si>
   <si>
     <t>-R$ 21.084,57</t>
@@ -11111,7 +11111,7 @@
         <v>-123.8</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16587,7 +16587,7 @@
         <v>0</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21422,7 +21422,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21458,27 +21458,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>4266.8699999999999</v>
+      </c>
+      <c r="P159" s="5">
+        <v>4266.8699999999999</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0.050565062169149355</v>
+      </c>
+      <c r="R159" s="7">
+        <v>47</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.093023255813953432</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27884273483841782</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.013582391776641896</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.046479620893066814</v>
+      </c>
+      <c r="W159" s="6">
+        <v>-0.00038845805004605248</v>
+      </c>
+      <c r="X159" s="8">
+        <v>30.253125000000001</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.65625</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>6.1739130434782608</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>6.4144433333333337</v>
+      </c>
       <c r="AC159" s="8">
         <v>13.243088999999999</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>19.618749999999999</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.40625</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>0</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 569.249,16</t>
-  </si>
-  <si>
-    <t>R$ 3.093,75
-R$ 3.195,92</t>
-  </si>
-  <si>
-    <t>0.6%
-3.1%</t>
+171</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 571.511,55</t>
+  </si>
+  <si>
+    <t>R$ 3.089,25
+R$ 3.190,46</t>
+  </si>
+  <si>
+    <t>0.3%
+2.8%</t>
   </si>
   <si>
     <t>36.7</t>
   </si>
   <si>
-    <t>(1.8%)</t>
-  </si>
-  <si>
-    <t>1849.0%</t>
-  </si>
-  <si>
-    <t>1800.4%</t>
+    <t>(2.0%)</t>
+  </si>
+  <si>
+    <t>1832.9%</t>
+  </si>
+  <si>
+    <t>1784.4%</t>
   </si>
   <si>
     <t>4.6%</t>
@@ -971,7 +971,7 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>75.6%</t>
+    <t>75.5%</t>
   </si>
   <si>
     <t>-R$ 21.084,57</t>
@@ -4876,7 +4876,7 @@
         <v>-84.700000000000003</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12674,7 +12674,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12708,25 +12708,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>2262.3899999999999</v>
+      </c>
+      <c r="P89" s="5">
+        <v>2262.3899999999999</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.41846704314991556</v>
+      </c>
+      <c r="R89" s="7">
+        <v>25</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.40476190476190477</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-22.059540309142104</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-22.3770894496528</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.044572111793280557</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.00097220196341037579</v>
+      </c>
+      <c r="X89" s="8">
+        <v>24.5303</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>4.6794884615384618</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>6.3499999999999996</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>17.849999999999998</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.63636363636363635</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14256,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -24754,7 +24788,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25701,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27008,7 +27042,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28417,7 +28451,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-05).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 571.511,55</t>
-  </si>
-  <si>
-    <t>R$ 3.089,25
-R$ 3.190,46</t>
-  </si>
-  <si>
-    <t>0.3%
-2.8%</t>
-  </si>
-  <si>
-    <t>36.7</t>
-  </si>
-  <si>
-    <t>(2.0%)</t>
-  </si>
-  <si>
-    <t>1832.9%</t>
-  </si>
-  <si>
-    <t>1784.4%</t>
+176</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 581.402,99</t>
+  </si>
+  <si>
+    <t>R$ 3.060,02
+R$ 3.156,02</t>
+  </si>
+  <si>
+    <t>(0.1%)
+2.2%</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>(2.5%)</t>
+  </si>
+  <si>
+    <t>1802.2%</t>
+  </si>
+  <si>
+    <t>1754.0%</t>
   </si>
   <si>
     <t>4.6%</t>
@@ -950,31 +950,31 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>26.1</t>
-  </si>
-  <si>
-    <t>74.0%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
   </si>
   <si>
     <t>4.7</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>11.6</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>75.5%</t>
-  </si>
-  <si>
-    <t>-R$ 21.084,57</t>
+    <t>6.9</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>75.9%</t>
+  </si>
+  <si>
+    <t>-R$ 21.040,57</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7920,7 +7920,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7956,25 +7956,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>206.40000000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>206.40000000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.70917288995350147</v>
+      </c>
+      <c r="R51" s="7">
+        <v>2</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.7142857142857143</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.27393410852713179</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.18113372093023256</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.43906976744186044</v>
+      </c>
+      <c r="X51" s="8">
+        <v>19.533349999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>7.0083500000000001</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>3.4833500000000002</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>17.38335</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8847,7 +8881,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.342791999999999</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20516,7 +20552,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20552,25 +20588,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>2395.48</v>
+      </c>
+      <c r="P151" s="5">
+        <v>2395.48</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.12625063375170065</v>
+      </c>
+      <c r="R151" s="7">
+        <v>27</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.22857142857142854</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.18931312304840783</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.11594093876801309</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.069729031342361456</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.018378153856429609</v>
+      </c>
+      <c r="X151" s="8">
+        <v>24.511665000000001</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.4265444444444446</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.6100000000000003</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>7.7541659999999997</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>14.711665</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21266,7 +21338,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21302,25 +21374,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>1636.45</v>
+      </c>
+      <c r="P157" s="5">
+        <v>1636.45</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.059773985687918918</v>
+      </c>
+      <c r="R157" s="7">
+        <v>22</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.047619047619047672</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.30750802041003389</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.0088658376363469696</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.084336215588621713</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.029730208683430598</v>
+      </c>
+      <c r="X157" s="8">
+        <v>24.698715384615387</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>7.9464894736842115</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.0628230769230766</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>10.899998999999999</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>17.839746153846153</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.76923076923076927</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21361,7 +21469,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21397,25 +21505,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>1919.6199999999999</v>
+      </c>
+      <c r="P158" s="5">
+        <v>1919.6199999999999</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.2440685041013464</v>
+      </c>
+      <c r="R158" s="7">
+        <v>23</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.28173263458392811</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.011090528333732719</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.055359133578520757</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.045077411154290953</v>
+      </c>
+      <c r="X158" s="8">
+        <v>21.632405555555557</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>3.8363636363636364</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>2.2907388888888889</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>6.3768510000000003</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>13.332405555555557</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22222,7 +22366,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22258,25 +22402,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>3733.4899999999998</v>
+      </c>
+      <c r="P165" s="5">
+        <v>3733.4899999999998</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.24287180194357472</v>
+      </c>
+      <c r="R165" s="7">
+        <v>44</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.32307692307692304</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.31803883229900176</v>
+      </c>
+      <c r="U165" s="6">
+        <v>0.0013806920602439006</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.024785120624402371</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.011165156462184177</v>
+      </c>
+      <c r="X165" s="8">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>3.8511904761904763</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>0.84277666666666673</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>5.1011100000000003</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>12.051666666666668</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>44</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
